--- a/players pool.xlsx
+++ b/players pool.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\draft game\2.1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GreenTech\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE8CEDC-F737-413E-A8E6-975A97844C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C01AE1F-1120-416A-9582-A66526FE282A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5990ED1F-368C-4CBF-8ACD-406B5FA8EFC9}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="707">
   <si>
     <t>Name</t>
   </si>
@@ -91,9 +91,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4f/Alisson_Becker_Brazil_V_Morocco_13_June_2026-117_%28cropped%29.jpg/960px-Alisson_Becker_Brazil_V_Morocco_13_June_2026-117_%28cropped%29.jpg</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/c4/Courtois_2018_%28cropped%29.jpg</t>
-  </si>
-  <si>
     <t>Oliver Kahn</t>
   </si>
   <si>
@@ -565,9 +562,6 @@
     <t>Patrick Vieira</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/6c/Patrick_Vieira_NYCFC_%28cropped%29.JPG</t>
-  </si>
-  <si>
     <t>Roy Keane</t>
   </si>
   <si>
@@ -598,9 +592,6 @@
     <t>Florian Wirtz</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Florian_Wirtz_Ecuador_v_Germany_25_June_2026-181_%28cropped%29.jpg/960px-Florian_Wirtz_Ecuador_v_Germany_25_June_2026-181_%28cropped%29.jpg</t>
-  </si>
-  <si>
     <t>Bernardo Silva</t>
   </si>
   <si>
@@ -1747,9 +1738,6 @@
     <t>Sócrates</t>
   </si>
   <si>
-    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcROkQZAHCy3DNBeB6F1FWoxC2ANPmZTwsaTh8iYjpdlyw&amp;s=10</t>
-  </si>
-  <si>
     <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ-L6wavH1tLISGXVQ3lWWInWdkIW3ISqw5VfvNXUUzjQ&amp;s=10</t>
   </si>
   <si>
@@ -1856,6 +1844,303 @@
   </si>
   <si>
     <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRpsoe4hCJCERAA6g3yxw2By29RMaIuRQD4RMfb8mu6zw&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSJeve1mzy0icQm9tIvWEkDvRcJLmrrZ5rc3nZWL-JraA&amp;s=10</t>
+  </si>
+  <si>
+    <t>Dino Zoff</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTx2hQdYqRZpQqjh_5VjJDIN82KEuJC8Z6OuEyyqms1zQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Jordan Pickford</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcREl70pNVpVmeEa21O5x8Kxeo8BelDUjyvAKKH5dMFPLA&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQmvnsozXqFeGFMYETDg9r0re6XiDpg6NO1dS33jaVJuQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Matvéi Safónov</t>
+  </si>
+  <si>
+    <t>Kasper Schmeichel</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR_avuMMuDOH0jx0R9gbwxCRZU4WxU42L6fY7_JaAU9aw&amp;s=10</t>
+  </si>
+  <si>
+    <t>Essam El-Hadary</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTrRjXUibXt5OaielJFdPsegFpa_j0G5pY7jMy879hNNQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Jorge Campos</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQlrZW9sBcnvcbjka5Vi1UU6sft_XoZnXzzdDj8XRpbww&amp;s=10</t>
+  </si>
+  <si>
+    <t>Hugo Lloris</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRRdk5LqXJ9K5uDE8R2op3WWgglpTJDmWjuC4-s7mV_ZA&amp;s=10</t>
+  </si>
+  <si>
+    <t>fabien barthez</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcR0g2EvfG27QZHqCKChAVQv-gaJkk1w6psSUAXpQF0iPQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Diogo Costa</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWsG6zeAC0YtrGtH3OH9dWkf7Fd57OCy1jq4FHGQ1Zqg&amp;s=10</t>
+  </si>
+  <si>
+    <t>Nicolò Barella</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQtOAQdK_0LH60W3-Yyic6YkfQqa9nWgntiEd0ag0Mdfg&amp;s=10</t>
+  </si>
+  <si>
+    <t>Aurélien Tchouaméni</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSvkeivN3jkqnNZn0s8_ZvrVR9I1GlW7nV_j65bxFW4kw&amp;s=10</t>
+  </si>
+  <si>
+    <t>Eduardo Camavinga</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRKsngJj3NGEwkqNNLuNcWijqIJPhdGCJHhEE_xHooJMg&amp;s=10</t>
+  </si>
+  <si>
+    <t>Hakan Çalhanoğlu</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTW-tkDpihHU_pm8wcthd4Rl_gUq6aahOsG1fCvpa3sDw&amp;s=10</t>
+  </si>
+  <si>
+    <t>Ryan Gravenberch</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQ7OmvrYcX_K_Qxw8hVE_KIuuO4_QhKZ0-Q4yyOPvgaYA&amp;s=10</t>
+  </si>
+  <si>
+    <t>Dominik Szoboszlai</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQYYtjX7Wy6BIlfvmEeluuCNTI7yiUlHwYrpbQNT25DBA&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTFmda3iD246I4UVsZocLMVRq-5IUb6aaHawhG57pbdWQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Enzo Fernández</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTQJe0l4KT9I9MnfVpajN4ob8gIuaSI_A0mTvtMUnJa0g&amp;s=10</t>
+  </si>
+  <si>
+    <t>Gennaro Gattuso</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRZ_yKFRiMTPWYbcoAEhEzmW1NKhWr3GSfsTm1w93kqtQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Claude Makélélé</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRPMn5v_WQ7eIW9Viwc_9Lc_s23TmZVct9hlAw4ANm4Ig&amp;s=10</t>
+  </si>
+  <si>
+    <t>Mesut Özil</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSsCAH-paHvBndNoP1jLnu4zkjZZ7FDYdBxDNqyytK_bQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Javier Mascherano</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRX39jVeV2nvMqprr9DDfvDMqqiBhgkD2FSWAv1K8eIew&amp;s=10</t>
+  </si>
+  <si>
+    <t>Gilberto Silva</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTgR04UtX2ccoRVaLPP0RKa6_kCnjujxY2X2ApxqfPeKg&amp;s=10</t>
+  </si>
+  <si>
+    <t>Dunga</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSZ7eCbcg7UNCngr4XUR0Bmn3O0486I9pbTJcSwuM_MNw&amp;s=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alfredo Di Stéfano</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT0g66iDvPBNbrCTRbedGh0tswiIQ1JnvcbCB5yEPCfLw&amp;s=10</t>
+  </si>
+  <si>
+    <t>Bobby Charlton</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSZKxyuhWvWzPrz0mjtf8o2v-2kH3m7m_PO3UEBC6It-A&amp;s=10</t>
+  </si>
+  <si>
+    <t>Bobby Moore</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT5Ex_dLnHZXOlIrMryxkQobJgC7L5S9wbdPiJ7rCiBSw&amp;s=10</t>
+  </si>
+  <si>
+    <t>Michael Laudrup</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT1TnI002KJ-R-1xdQDdfn-kGYqXcDRvLLSXEMY8HPpzg&amp;s=10</t>
+  </si>
+  <si>
+    <t>João Neves</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcT0Wfny6hkuy6DhttQqh9wJD-pl6v4d9AbBAgrs5TpGGA&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRSZ3ICruc5S10SWSC_hE37WersN1aDnRSlsqnK1Ngv7w&amp;s=10</t>
+  </si>
+  <si>
+    <t>Romário</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQPdQ4Hm4xW6H69JXQDYqwflF4u6RCCv3RViQaMTltowA&amp;s=10</t>
+  </si>
+  <si>
+    <t>Andriy Shevchenko</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSdV2cM683NLfi-22_ACXXSNx8YiS4BOd_SJYN8uNGIuQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Emilio Butragueño</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSVEff6jOWyX8mLJ2E1jq7n_F2s0HnKN44DHD0y8v8fFA&amp;s=10</t>
+  </si>
+  <si>
+    <t>Alan Shearer</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTmO4URUJXXHX8aeseGGFJX7qIbvjfwx4qhHEKsSUER5Q&amp;s=10</t>
+  </si>
+  <si>
+    <t>Iván Córdoba</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS6oN17VIGQyib2FlCYX-ZWfajLePNH2bmunlQ3PRbxFQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Ledley King</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQRu2NIqaZE4UeBnn2vaWVn8eVrukJ_cEQ2oloVZeh1fA&amp;s=10</t>
+  </si>
+  <si>
+    <t>Emmanuel Petit</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS50fPY3VbjKgAc81hqN1xFQZwvqli3yqIR2cJZE-GKWg&amp;s=10</t>
+  </si>
+  <si>
+    <t>David Villa</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRiPlvke9l-9tYg2fGznC7rZTxeFYX22391i8lUKkQz9Q&amp;s</t>
+  </si>
+  <si>
+    <t>Antoine Griezmann</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQNsgHS-5C4-L7ULyGHxgCeREKIjGdvxwv7bktjNjJBpA&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSQZ5ZN90yIw71LPgap4JWkSTMzP7x4Dm5N4wrYAWh0eg&amp;s=10</t>
+  </si>
+  <si>
+    <t>Kenny Dalglish</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSRF0CEd25QhcQ-ow56kZ9Hh6VSl89OCt1celqtPUwVVw&amp;s=10</t>
+  </si>
+  <si>
+    <t>George Weah</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSNMFfUUoMKaF6KsDEqLuY5x5fTtfY9tp29eDTRBIbnhg&amp;s=10</t>
+  </si>
+  <si>
+    <t>Karl-Heinz Rummenigge</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRNeDPbsEAul04DDDsN8RuiLWmC-q6GPKeFyLR07P9e_g&amp;s=10</t>
+  </si>
+  <si>
+    <t>Jairzinho</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcStVBP9fye2J6hIHQ815vmCWsG8CJyj4hXdWC0c6LoqNQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>Peter Crouch</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQRqjLSA0y_C47eVpg6AGbQ9JRJfdbbfqFuhl4J550a-A&amp;s=10</t>
+  </si>
+  <si>
+    <t>Jan Koller</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSrNoxbKwtRQUY8VB8fSCfbP5di3Iqc0dPWrxfRd3Q5fw&amp;s=10</t>
+  </si>
+  <si>
+    <t>Vicente Del Bosque</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQvodHpVvMlYOQ6tuLEJSdlX0hsFCBGm6HNulTmuWd0YA&amp;s=10</t>
+  </si>
+  <si>
+    <t>Arsene Wenger</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQCUwXgSnGMZpu9iHawwfMo7DaOw99LJxA2kt8TnsWO1w&amp;s=10</t>
+  </si>
+  <si>
+    <t>bob paisley</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQHlf_PURX1HO9J6P0JQGhfQTY5pv9vsKqAtKo-vLnksg&amp;s=10</t>
+  </si>
+  <si>
+    <t>Hansi Flick</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQvOnU4w1LhGGE0OJ9dKwEVCifRCEajG2DKezkKqnl5zg&amp;s=10</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQhY5l_QtOFDCX_-7Sw63NT_2mV9m-fg0vScfrSDF0uiw&amp;s=10</t>
+  </si>
+  <si>
+    <t>Luis de la Fuente</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcS77Nu05SgDFx29lFHrKAuS_iOQRXMXVUXBTFx9D-FygA&amp;s=10</t>
   </si>
 </sst>
 </file>
@@ -2786,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9175D811-F6EA-4D84-8470-E8C9AAFCD7D9}">
-  <dimension ref="A1:C305"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2819,7 +3104,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2862,1248 +3147,1248 @@
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>23</v>
+      <c r="C7" s="3" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>611</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>614</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>615</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>616</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>617</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>29</v>
+      <c r="C12" s="3" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>619</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>326</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>621</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>32</v>
+      <c r="C14" s="3" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>327</v>
+        <v>623</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>328</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>625</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>34</v>
+      <c r="C16" s="3" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>589</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>36</v>
+      <c r="C17" s="3" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>38</v>
+      <c r="C18" s="3" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>40</v>
+      <c r="C19" s="3" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>42</v>
+      <c r="C20" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>46</v>
+      <c r="C22" s="3" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>329</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>334</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>335</v>
+      <c r="C24" s="3" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>331</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>336</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>332</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>337</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>333</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>338</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" thickBot="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" thickBot="1">
-      <c r="A31" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>357</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>326</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>55</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>327</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>57</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>359</v>
+        <v>4</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>329</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>495</v>
+        <v>330</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>496</v>
+        <v>4</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>497</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>521</v>
+        <v>49</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>47</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" thickBot="1">
       <c r="A39" s="1" t="s">
-        <v>526</v>
+        <v>51</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" thickBot="1">
+      <c r="A40" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>528</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>530</v>
+        <v>53</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>529</v>
+        <v>47</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>531</v>
+        <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>532</v>
+        <v>47</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>533</v>
+        <v>355</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>534</v>
+        <v>356</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>535</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>536</v>
+        <v>47</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>537</v>
+        <v>492</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>538</v>
+        <v>493</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>539</v>
+        <v>494</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>540</v>
+        <v>495</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>532</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>47</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>534</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="1" t="s">
-        <v>64</v>
+        <v>536</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="1" t="s">
-        <v>66</v>
+        <v>538</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="1" t="s">
-        <v>68</v>
+        <v>540</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>69</v>
+        <v>47</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>673</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="1" t="s">
-        <v>72</v>
+        <v>675</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>73</v>
+        <v>47</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
-        <v>360</v>
+        <v>542</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>361</v>
+        <v>543</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="1" t="s">
-        <v>74</v>
+        <v>544</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="1" t="s">
-        <v>76</v>
+        <v>546</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>77</v>
+        <v>47</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>658</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="1" t="s">
-        <v>362</v>
+        <v>548</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>369</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
-        <v>363</v>
+        <v>59</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>370</v>
+        <v>47</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="1" t="s">
-        <v>364</v>
+        <v>61</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>371</v>
+        <v>47</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="1" t="s">
-        <v>365</v>
+        <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>372</v>
+        <v>47</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1" t="s">
-        <v>366</v>
+        <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>373</v>
+        <v>47</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
-        <v>367</v>
+        <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>374</v>
+        <v>47</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>368</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>375</v>
+        <v>47</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>83</v>
+        <v>47</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>610</v>
+        <v>47</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="1" t="s">
-        <v>90</v>
+        <v>359</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="1" t="s">
-        <v>91</v>
+        <v>361</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>92</v>
+        <v>47</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="1" t="s">
-        <v>93</v>
+        <v>362</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="1" t="s">
-        <v>95</v>
+        <v>363</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>96</v>
+        <v>47</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="1" t="s">
-        <v>97</v>
+        <v>364</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>98</v>
+        <v>47</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="1" t="s">
-        <v>99</v>
+        <v>365</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="1" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="1" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="1" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>377</v>
+        <v>606</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="1" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="1" t="s">
-        <v>112</v>
+        <v>383</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="1" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="1" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="1" t="s">
-        <v>378</v>
+        <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>379</v>
+        <v>88</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
-        <v>380</v>
+        <v>96</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>381</v>
+        <v>88</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="1" t="s">
-        <v>383</v>
+        <v>98</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>384</v>
+        <v>88</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="1" t="s">
-        <v>382</v>
+        <v>100</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>385</v>
+        <v>88</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="1" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="1" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="1" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="1" t="s">
-        <v>135</v>
+        <v>375</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>136</v>
+        <v>88</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="1" t="s">
-        <v>137</v>
+        <v>377</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>138</v>
+        <v>88</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="1" t="s">
-        <v>139</v>
+        <v>380</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>140</v>
+        <v>88</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="1" t="s">
-        <v>135</v>
+        <v>379</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="1" t="s">
-        <v>391</v>
+        <v>117</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>392</v>
+        <v>88</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
-        <v>393</v>
+        <v>119</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>394</v>
+        <v>88</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>121</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="1" t="s">
-        <v>397</v>
+        <v>124</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>396</v>
+        <v>122</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>388</v>
+        <v>122</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="1" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="1" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="1" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="1" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="1" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="1" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>155</v>
+        <v>122</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="1" t="s">
-        <v>156</v>
+        <v>388</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>389</v>
@@ -4111,2200 +4396,2787 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="1" t="s">
-        <v>522</v>
+        <v>390</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>523</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="1" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>158</v>
+        <v>122</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="1" t="s">
-        <v>159</v>
+        <v>394</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>160</v>
+        <v>122</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="1" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="1" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>399</v>
+        <v>122</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="1" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>400</v>
+        <v>122</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="1" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
-        <v>427</v>
+        <v>151</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>428</v>
+        <v>122</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="1" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>173</v>
+        <v>122</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="1" t="s">
-        <v>174</v>
+        <v>519</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>175</v>
+        <v>122</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="1" t="s">
-        <v>404</v>
+        <v>158</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>405</v>
+        <v>122</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="1" t="s">
-        <v>406</v>
+        <v>19</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="1" t="s">
-        <v>409</v>
+        <v>161</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>408</v>
+        <v>160</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="1" t="s">
-        <v>410</v>
+        <v>163</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="1" t="s">
-        <v>412</v>
+        <v>164</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>413</v>
+        <v>160</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="1" t="s">
-        <v>414</v>
+        <v>166</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="1" t="s">
-        <v>416</v>
+        <v>167</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>417</v>
+        <v>160</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
-        <v>418</v>
+        <v>677</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>419</v>
+        <v>678</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="1" t="s">
-        <v>184</v>
+        <v>424</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="1" t="s">
-        <v>402</v>
+        <v>169</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>403</v>
+        <v>160</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="1" t="s">
-        <v>553</v>
+        <v>627</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>554</v>
+        <v>628</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="1" t="s">
-        <v>555</v>
+        <v>629</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>556</v>
+        <v>630</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="1" t="s">
-        <v>557</v>
+        <v>631</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>558</v>
+        <v>632</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="1" t="s">
-        <v>180</v>
+        <v>633</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>559</v>
+        <v>634</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="1" t="s">
-        <v>560</v>
+        <v>635</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>561</v>
+        <v>636</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
-        <v>562</v>
+        <v>637</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>563</v>
+        <v>638</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="1" t="s">
-        <v>564</v>
+        <v>640</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>565</v>
+        <v>641</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="1" t="s">
-        <v>566</v>
+        <v>642</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>567</v>
+        <v>643</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="1" t="s">
-        <v>568</v>
+        <v>644</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>569</v>
+        <v>645</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="1" t="s">
-        <v>570</v>
+        <v>646</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>571</v>
+        <v>647</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="1" t="s">
-        <v>572</v>
+        <v>648</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>573</v>
+        <v>649</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="1" t="s">
-        <v>574</v>
+        <v>650</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>575</v>
+        <v>651</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="1" t="s">
-        <v>591</v>
+        <v>652</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>592</v>
+        <v>653</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
-        <v>577</v>
+        <v>654</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>576</v>
+        <v>655</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="1" t="s">
-        <v>578</v>
+        <v>656</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>579</v>
+        <v>657</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="1" t="s">
-        <v>191</v>
+        <v>660</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>580</v>
+        <v>661</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="1" t="s">
-        <v>178</v>
+        <v>662</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="1" t="s">
-        <v>425</v>
+        <v>171</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>426</v>
+        <v>160</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="1" t="s">
-        <v>421</v>
+        <v>173</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>424</v>
+        <v>160</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="1" t="s">
-        <v>422</v>
+        <v>175</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>423</v>
+        <v>160</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="1" t="s">
-        <v>180</v>
+        <v>401</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>181</v>
+        <v>160</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
-        <v>182</v>
+        <v>403</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="1" t="s">
-        <v>184</v>
+        <v>406</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="1" t="s">
-        <v>186</v>
+        <v>407</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="1" t="s">
-        <v>187</v>
+        <v>409</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>188</v>
+        <v>160</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="1" t="s">
-        <v>189</v>
+        <v>411</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>190</v>
+        <v>160</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="1" t="s">
-        <v>191</v>
+        <v>413</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>192</v>
+        <v>160</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="1" t="s">
-        <v>193</v>
+        <v>415</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>194</v>
+        <v>160</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="1" t="s">
-        <v>434</v>
+        <v>182</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
-        <v>195</v>
+        <v>399</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>196</v>
+        <v>160</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="1" t="s">
-        <v>197</v>
+        <v>550</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>198</v>
+        <v>160</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="1" t="s">
-        <v>233</v>
+        <v>552</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>234</v>
+        <v>160</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="1" t="s">
-        <v>227</v>
+        <v>554</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>228</v>
+        <v>160</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="1" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>200</v>
+        <v>160</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="1" t="s">
-        <v>201</v>
+        <v>557</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>202</v>
+        <v>160</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="1" t="s">
-        <v>203</v>
+        <v>559</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>204</v>
+        <v>160</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="1" t="s">
-        <v>205</v>
+        <v>561</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
-        <v>207</v>
+        <v>563</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>208</v>
+        <v>160</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="1" t="s">
-        <v>209</v>
+        <v>565</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>210</v>
+        <v>160</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="1" t="s">
-        <v>211</v>
+        <v>567</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>212</v>
+        <v>160</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="1" t="s">
-        <v>213</v>
+        <v>569</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>214</v>
+        <v>160</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="1" t="s">
-        <v>215</v>
+        <v>571</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>216</v>
+        <v>160</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
-        <v>217</v>
+        <v>587</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>218</v>
+        <v>160</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="1" t="s">
-        <v>219</v>
+        <v>573</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>220</v>
+        <v>160</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="1" t="s">
-        <v>221</v>
+        <v>574</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>222</v>
+        <v>160</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="1" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>224</v>
+        <v>160</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="1" t="s">
-        <v>242</v>
+        <v>422</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>243</v>
+        <v>160</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" s="1" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C193" s="6" t="s">
-        <v>430</v>
+        <v>160</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="1" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C194" s="6" t="s">
-        <v>438</v>
+        <v>160</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="1" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C195" s="6" t="s">
-        <v>439</v>
+        <v>160</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="1" t="s">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>431</v>
+        <v>160</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" s="1" t="s">
-        <v>252</v>
+        <v>681</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>611</v>
+        <v>682</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" s="1" t="s">
-        <v>253</v>
+        <v>184</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" s="1" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>257</v>
+        <v>188</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" s="1" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>259</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" s="1" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="1" t="s">
-        <v>261</v>
+        <v>192</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" s="1" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" s="1" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" s="1" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>268</v>
+        <v>225</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
-        <v>269</v>
+        <v>196</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" s="1" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="1" t="s">
-        <v>273</v>
+        <v>200</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="1" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>436</v>
+        <v>248</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="1" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>277</v>
+        <v>205</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="1" t="s">
-        <v>278</v>
+        <v>206</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>279</v>
+        <v>207</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="1" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="1" t="s">
-        <v>282</v>
+        <v>210</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>440</v>
+        <v>248</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
-        <v>284</v>
+        <v>212</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C215" s="3" t="s">
-        <v>441</v>
+        <v>248</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="1" t="s">
-        <v>285</v>
+        <v>214</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>286</v>
+        <v>215</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="1" t="s">
-        <v>287</v>
+        <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="1" t="s">
-        <v>289</v>
+        <v>218</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>290</v>
+        <v>219</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="1" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>292</v>
+        <v>221</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="1" t="s">
-        <v>293</v>
+        <v>222</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>294</v>
+        <v>223</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="1" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="1" t="s">
-        <v>303</v>
+        <v>426</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>494</v>
+        <v>248</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
-        <v>499</v>
+        <v>434</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>500</v>
+        <v>248</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="1" t="s">
-        <v>501</v>
+        <v>253</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>502</v>
+        <v>248</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" s="1" t="s">
-        <v>503</v>
+        <v>247</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>504</v>
+        <v>428</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" s="1" t="s">
-        <v>505</v>
+        <v>249</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>506</v>
+        <v>607</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="1" t="s">
-        <v>507</v>
+        <v>250</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>508</v>
+        <v>429</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="1" t="s">
-        <v>509</v>
+        <v>251</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>510</v>
+        <v>248</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="1" t="s">
-        <v>515</v>
+        <v>253</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>516</v>
+        <v>248</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="1" t="s">
-        <v>517</v>
+        <v>255</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>518</v>
+        <v>248</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
-        <v>519</v>
+        <v>257</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>520</v>
+        <v>430</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="1" t="s">
-        <v>511</v>
+        <v>258</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>512</v>
+        <v>248</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" s="1" t="s">
-        <v>513</v>
+        <v>260</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>514</v>
+        <v>248</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" s="1" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="1" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="1" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="1" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="1" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="1" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C242" s="2" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="1" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>300</v>
+        <v>280</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
-        <v>449</v>
+        <v>281</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="1" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C245" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>442</v>
+        <v>280</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" s="1" t="s">
-        <v>443</v>
+        <v>286</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C247" s="3" t="s">
-        <v>444</v>
+        <v>280</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
-        <v>445</v>
+        <v>288</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>446</v>
+        <v>280</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" s="1" t="s">
-        <v>447</v>
+        <v>690</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>448</v>
+        <v>691</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" s="1" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C250" s="3" t="s">
-        <v>451</v>
+        <v>280</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C251" s="3" t="s">
-        <v>452</v>
+        <v>280</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>453</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" s="1" t="s">
-        <v>307</v>
+        <v>496</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>308</v>
+        <v>280</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" s="1" t="s">
-        <v>309</v>
+        <v>498</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>454</v>
+        <v>499</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" s="1" t="s">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>455</v>
+        <v>501</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
-        <v>11</v>
+        <v>502</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>456</v>
+        <v>503</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" s="1" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" s="1" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" s="1" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>466</v>
+        <v>513</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" s="1" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>468</v>
+        <v>515</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" s="1" t="s">
-        <v>469</v>
+        <v>516</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>471</v>
+        <v>517</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" s="1" t="s">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>472</v>
+        <v>509</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" s="1" t="s">
-        <v>344</v>
+        <v>510</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>473</v>
+        <v>511</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
-        <v>474</v>
+        <v>294</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>475</v>
+        <v>280</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" s="1" t="s">
-        <v>478</v>
+        <v>232</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>479</v>
+        <v>280</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" s="1" t="s">
-        <v>492</v>
+        <v>235</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>493</v>
+        <v>280</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" s="1" t="s">
-        <v>480</v>
+        <v>237</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C267" s="3" t="s">
-        <v>481</v>
+        <v>280</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" s="1" t="s">
-        <v>482</v>
+        <v>226</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>483</v>
+        <v>280</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
-        <v>484</v>
+        <v>228</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>485</v>
+        <v>280</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" s="1" t="s">
-        <v>486</v>
+        <v>241</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>489</v>
+        <v>280</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" s="1" t="s">
-        <v>487</v>
+        <v>243</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>488</v>
+        <v>280</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" s="1" t="s">
-        <v>476</v>
+        <v>245</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C272" s="3" t="s">
-        <v>477</v>
+        <v>280</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
-        <v>490</v>
+        <v>296</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C273" s="3" t="s">
-        <v>491</v>
+        <v>280</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" s="1" t="s">
-        <v>13</v>
+        <v>446</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" s="1" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C275" s="3" t="s">
-        <v>458</v>
+        <v>280</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" s="1" t="s">
-        <v>14</v>
+        <v>284</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>312</v>
+        <v>280</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" s="1" t="s">
-        <v>15</v>
+        <v>440</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" s="1" t="s">
-        <v>16</v>
+        <v>442</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>313</v>
+        <v>280</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" s="1" t="s">
-        <v>314</v>
+        <v>444</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>315</v>
+        <v>280</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" s="1" t="s">
-        <v>17</v>
+        <v>301</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
-        <v>18</v>
+        <v>302</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C281" s="2" t="s">
-        <v>316</v>
+      <c r="C281" s="3" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" s="1" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C282" s="2" t="s">
-        <v>318</v>
+      <c r="C282" s="3" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" s="1" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C284" s="2" t="s">
-        <v>322</v>
+      <c r="C284" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" s="1" t="s">
-        <v>583</v>
+        <v>307</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>584</v>
+        <v>452</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" s="1" t="s">
-        <v>590</v>
+        <v>11</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>589</v>
+        <v>453</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" s="1" t="s">
-        <v>585</v>
+        <v>458</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>586</v>
+        <v>459</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" s="1" t="s">
-        <v>587</v>
+        <v>460</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>588</v>
+        <v>461</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
-        <v>581</v>
+        <v>462</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>582</v>
+        <v>463</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" s="1" t="s">
-        <v>323</v>
+        <v>464</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C290" s="2" t="s">
-        <v>324</v>
+      <c r="C290" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B291" t="s">
-        <v>348</v>
+        <v>466</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>355</v>
+        <v>468</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B292" t="s">
-        <v>348</v>
+        <v>467</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>354</v>
+        <v>469</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B293" t="s">
-        <v>348</v>
+      <c r="B293" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>353</v>
+        <v>470</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B294" t="s">
-        <v>348</v>
+        <v>471</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>352</v>
+        <v>472</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="B295" t="s">
-        <v>348</v>
+        <v>475</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>351</v>
+        <v>476</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B296" t="s">
-        <v>348</v>
+        <v>489</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>350</v>
+        <v>490</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B297" t="s">
-        <v>348</v>
+        <v>477</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>349</v>
+        <v>478</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B298" t="s">
-        <v>348</v>
+        <v>479</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>347</v>
+        <v>480</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="B299" t="s">
-        <v>348</v>
+        <v>481</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>596</v>
+        <v>482</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="B300" t="s">
-        <v>348</v>
+        <v>483</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>598</v>
+        <v>486</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B301" t="s">
-        <v>348</v>
+        <v>484</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>602</v>
+        <v>485</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="B302" t="s">
-        <v>348</v>
+        <v>473</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>601</v>
+        <v>474</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="B303" t="s">
-        <v>348</v>
+        <v>487</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>604</v>
+        <v>488</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="B304" t="s">
-        <v>348</v>
+        <v>13</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>606</v>
+        <v>454</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" t="s">
+        <v>345</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B334" t="s">
+        <v>345</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B335" t="s">
+        <v>345</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B336" t="s">
+        <v>345</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337" t="s">
+        <v>345</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B338" t="s">
+        <v>345</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B339" t="s">
+        <v>345</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B340" t="s">
+        <v>345</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B341" t="s">
+        <v>345</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B342" t="s">
+        <v>345</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B343" t="s">
+        <v>345</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B344" t="s">
+        <v>345</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B345" t="s">
+        <v>345</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B346" t="s">
+        <v>345</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B305" t="s">
-        <v>348</v>
-      </c>
-      <c r="C305" s="3" t="s">
-        <v>607</v>
-      </c>
+      <c r="B347" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" s="1"/>
+      <c r="B354" s="1"/>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" s="1"/>
+      <c r="B355" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{91794AFF-4AE4-40E5-9BC0-5B113C9EB83F}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{32FD0D2A-6C96-4E29-86F7-7F8379FA3E6F}"/>
-    <hyperlink ref="C13" r:id="rId3" xr:uid="{20733D4E-76EF-4D15-A191-DA273D019F1C}"/>
-    <hyperlink ref="C15" r:id="rId4" xr:uid="{8848D822-3821-4FB6-8AD3-8B584E94883B}"/>
-    <hyperlink ref="C298" r:id="rId5" xr:uid="{06B84589-7D92-4C6A-A1EC-D7F163E0D0DD}"/>
-    <hyperlink ref="C297" r:id="rId6" xr:uid="{2CDCECDC-EC23-45B2-83C3-6D858FBA83A4}"/>
-    <hyperlink ref="C296" r:id="rId7" xr:uid="{D66CABB6-8C01-408D-B0E5-66C569EA9218}"/>
-    <hyperlink ref="C295" r:id="rId8" xr:uid="{B8971A20-58A8-4C22-A9E8-91E87196AB83}"/>
-    <hyperlink ref="C294" r:id="rId9" xr:uid="{1EA17FF3-8048-41C4-823F-0DA5263637DC}"/>
-    <hyperlink ref="C293" r:id="rId10" xr:uid="{7AD84014-6533-40E3-9D98-4A265A3FDBD4}"/>
-    <hyperlink ref="C292" r:id="rId11" xr:uid="{B84975E4-7A1A-42CD-A0A0-537634E54280}"/>
-    <hyperlink ref="C291" r:id="rId12" xr:uid="{4200CE26-D6ED-4E3C-9775-C7598E4B6F49}"/>
-    <hyperlink ref="C31" r:id="rId13" xr:uid="{DE12AE35-6DEA-463D-B53F-2212C88645DB}"/>
-    <hyperlink ref="C34" r:id="rId14" xr:uid="{3B00C787-BB82-49CC-8A95-41EF4467A59B}"/>
-    <hyperlink ref="C60" r:id="rId15" xr:uid="{2AE76950-5324-4300-995E-5106A02D8E1B}"/>
-    <hyperlink ref="C65" r:id="rId16" xr:uid="{2D05523D-21DF-4F93-B581-B4A62EA2310C}"/>
-    <hyperlink ref="C64" r:id="rId17" xr:uid="{93E442DC-7068-437C-A8CE-29140B51D4A5}"/>
-    <hyperlink ref="C66" r:id="rId18" xr:uid="{8A555388-3D3D-4DF3-8F65-6B122CF52D40}"/>
-    <hyperlink ref="C67" r:id="rId19" xr:uid="{AF42E519-D7E9-4481-BCC9-2BC44CAEF483}"/>
-    <hyperlink ref="C68" r:id="rId20" xr:uid="{A5D2BDE3-4300-44D9-85CC-C36E56697508}"/>
-    <hyperlink ref="C69" r:id="rId21" xr:uid="{0EBE1D87-4A83-4F86-A580-529D6A6D6ADD}"/>
-    <hyperlink ref="C70" r:id="rId22" xr:uid="{D203E76E-29B6-4FAC-8DDF-41834DDFAB9F}"/>
-    <hyperlink ref="C76" r:id="rId23" xr:uid="{B86817D4-9E10-4D5C-A26A-EDF200C95CCD}"/>
-    <hyperlink ref="C87" r:id="rId24" xr:uid="{5E37B822-E937-4EA5-943F-4EEEA243B407}"/>
-    <hyperlink ref="C92" r:id="rId25" xr:uid="{5BABD35C-A539-45C6-BCC5-D1110132BD22}"/>
-    <hyperlink ref="C93" r:id="rId26" xr:uid="{94F74941-3E3B-4CB6-9101-B175F232B080}"/>
-    <hyperlink ref="C112" r:id="rId27" xr:uid="{516F9274-1601-4712-A989-FCCE247FC4E7}"/>
-    <hyperlink ref="C120" r:id="rId28" xr:uid="{2FA531D4-566E-4D78-99B3-CB6858F708F0}"/>
-    <hyperlink ref="C107" r:id="rId29" xr:uid="{BD966A3C-FFB2-48D6-A450-18F764AFF163}"/>
-    <hyperlink ref="C108" r:id="rId30" xr:uid="{40BACF63-FB50-44BA-9095-10B8796E4BE6}"/>
-    <hyperlink ref="C109" r:id="rId31" xr:uid="{821F58CC-BF96-4CA9-9FB2-A0F7FFCAFB35}"/>
-    <hyperlink ref="C110" r:id="rId32" xr:uid="{7604A04A-9CAD-433F-BE86-8E29D0ABDADB}"/>
-    <hyperlink ref="C111" r:id="rId33" xr:uid="{3BFDFFE0-C278-4A9B-B3AB-4797EB1254B3}"/>
-    <hyperlink ref="C124" r:id="rId34" xr:uid="{EE28E420-01EF-44B6-B677-A650514BEB32}"/>
-    <hyperlink ref="C126" r:id="rId35" xr:uid="{A395A8DF-3B2F-4066-A368-7DF3E8B68D5A}"/>
-    <hyperlink ref="C128" r:id="rId36" xr:uid="{2C402ADD-A9D7-4E73-9A47-00F715C5F723}"/>
-    <hyperlink ref="C168" r:id="rId37" xr:uid="{E1189F8B-D001-4C35-AA5B-0B8D78BC5764}"/>
-    <hyperlink ref="C144" r:id="rId38" xr:uid="{26D74A8A-C77D-4802-96E8-9CB5B9362A67}"/>
-    <hyperlink ref="C135" r:id="rId39" xr:uid="{EAA57945-F0B4-415F-92EC-8E043DA4011F}"/>
-    <hyperlink ref="C136" r:id="rId40" xr:uid="{D04D35D1-1A61-44A9-97FC-CF35B7483BA0}"/>
-    <hyperlink ref="C137" r:id="rId41" xr:uid="{DF4A7D14-251A-4379-A2DF-F79F25D5631B}"/>
-    <hyperlink ref="C138" r:id="rId42" xr:uid="{85EA1E54-06CF-42DF-B863-E17872EC7F9E}"/>
-    <hyperlink ref="C139" r:id="rId43" xr:uid="{6B74270E-8219-4E30-90C0-C8F8BB0F233E}"/>
-    <hyperlink ref="C140" r:id="rId44" xr:uid="{3B808E52-8245-42C5-8AB1-371B3426AB46}"/>
-    <hyperlink ref="C141" r:id="rId45" xr:uid="{57BE5715-6EB8-48AD-9D8E-68D2A2C1AC45}"/>
-    <hyperlink ref="C142" r:id="rId46" xr:uid="{F86C6EF3-29C2-4A55-B804-07AAADD2281A}"/>
-    <hyperlink ref="C143" r:id="rId47" xr:uid="{F316FF57-6B3C-4B4C-8570-0821DD015CA8}"/>
-    <hyperlink ref="C164" r:id="rId48" xr:uid="{627ADE43-952B-43B7-B0B5-14646496C762}"/>
-    <hyperlink ref="C163" r:id="rId49" xr:uid="{3AE9DF49-D95E-4C0B-81D9-2A6FBBF188B2}"/>
-    <hyperlink ref="C162" r:id="rId50" xr:uid="{BF206D77-8B0F-443A-AA07-E839166658AE}"/>
-    <hyperlink ref="C130" r:id="rId51" xr:uid="{A374E38A-D2A4-492A-8A27-453DB919A65E}"/>
-    <hyperlink ref="C193" r:id="rId52" xr:uid="{F8E60DA5-82F0-44D7-9BE0-1ECA3A1592D0}"/>
-    <hyperlink ref="C196" r:id="rId53" xr:uid="{B7D784B0-EB2B-4CD6-A69D-91AD2CF7650B}"/>
-    <hyperlink ref="C198" r:id="rId54" xr:uid="{345F84E1-725F-4245-8DAA-513D09173FA4}"/>
-    <hyperlink ref="C202" r:id="rId55" xr:uid="{006E2639-98C6-4267-B7E6-2D637FA75DB7}"/>
-    <hyperlink ref="C173" r:id="rId56" xr:uid="{3BAC8BD3-2588-4FE6-AEAD-45FF6DEDF142}"/>
-    <hyperlink ref="C210" r:id="rId57" xr:uid="{EFDA4C91-3EF0-4AE8-B57A-B62EBE338CF7}"/>
-    <hyperlink ref="C194" r:id="rId58" xr:uid="{17119B19-6319-4464-B49B-F5E05C0FBF16}"/>
-    <hyperlink ref="C195" r:id="rId59" xr:uid="{C186F788-2029-44BF-9BD8-2CEC23AFAFFB}"/>
-    <hyperlink ref="C214" r:id="rId60" xr:uid="{C992E7AC-77D1-4580-9587-D5DD3454903E}"/>
-    <hyperlink ref="C215" r:id="rId61" xr:uid="{72118CFF-73CF-44CE-824E-2C7A6FEC993B}"/>
-    <hyperlink ref="C246" r:id="rId62" xr:uid="{742B394F-41B4-4BD8-A7A1-5814B9A6F4B0}"/>
-    <hyperlink ref="C247" r:id="rId63" xr:uid="{4196C746-9A38-4CC2-9D9B-E9BD1DCB665D}"/>
-    <hyperlink ref="C248" r:id="rId64" xr:uid="{2A9F81E4-8C6A-4870-A6CC-9D02518EEC2C}"/>
-    <hyperlink ref="C249" r:id="rId65" xr:uid="{918A3F4A-38CF-48DC-B25E-8F8206F6A21A}"/>
-    <hyperlink ref="C244" r:id="rId66" xr:uid="{69C00299-FCDF-4809-9709-4758F63AA450}"/>
-    <hyperlink ref="C250" r:id="rId67" xr:uid="{8EEB60CE-4C22-48E8-9948-99D3F7910A9C}"/>
-    <hyperlink ref="C251" r:id="rId68" xr:uid="{AEBCC0BF-1011-4EC2-BDC2-FBC699536B01}"/>
-    <hyperlink ref="C252" r:id="rId69" xr:uid="{2BA6B95C-F5B6-492C-8DAD-FEB98442F16B}"/>
-    <hyperlink ref="C254" r:id="rId70" xr:uid="{996F9E28-A976-4136-9509-BA0FD9AFC609}"/>
-    <hyperlink ref="C255" r:id="rId71" xr:uid="{DC5D5DB2-0B42-4B48-82C1-B0B6CFBC6E53}"/>
-    <hyperlink ref="C256" r:id="rId72" xr:uid="{3FB19267-D7AF-4689-B824-E43DC189BD41}"/>
-    <hyperlink ref="C274" r:id="rId73" xr:uid="{7DCD7B89-333E-475A-86FC-B6C842E51B32}"/>
-    <hyperlink ref="C275" r:id="rId74" xr:uid="{DD6EA494-FA8C-4FA3-AFDA-3AAB807783C4}"/>
-    <hyperlink ref="C277" r:id="rId75" xr:uid="{FD57C63E-4A9E-44F3-A68D-7D89331A239F}"/>
-    <hyperlink ref="C280" r:id="rId76" xr:uid="{461E749D-72B1-43DA-AC45-1276B46CDE71}"/>
-    <hyperlink ref="C257" r:id="rId77" xr:uid="{10F07EE6-12D1-49B1-BE4D-0B960E4AB8C8}"/>
-    <hyperlink ref="C258" r:id="rId78" xr:uid="{B9D6B3F9-6330-475B-A5CB-C68860BF8F7F}"/>
-    <hyperlink ref="C259" r:id="rId79" xr:uid="{59EE37E4-067E-4B14-B37D-1A2BA9000586}"/>
-    <hyperlink ref="C260" r:id="rId80" xr:uid="{568FE7CE-3364-4CD6-AEFC-687097A104FF}"/>
-    <hyperlink ref="C261" r:id="rId81" xr:uid="{D92E157D-9FF5-4554-A712-3E76586EA7A9}"/>
-    <hyperlink ref="C262" r:id="rId82" xr:uid="{ADFB8930-804D-438B-BC6A-C3563EFA36F0}"/>
-    <hyperlink ref="C263" r:id="rId83" xr:uid="{7B2C9358-08A3-4414-85F3-1F82D40BCC3A}"/>
-    <hyperlink ref="C264" r:id="rId84" xr:uid="{C56446CA-EDC5-4121-A19D-ECBA57E3D5E0}"/>
-    <hyperlink ref="C272" r:id="rId85" xr:uid="{13EF1E40-B469-438B-9385-2AB7F8E3DEA1}"/>
-    <hyperlink ref="C265" r:id="rId86" xr:uid="{87150E4D-68B3-4113-88EA-A4FF14C6760A}"/>
-    <hyperlink ref="C267" r:id="rId87" xr:uid="{18681F76-D099-492A-A200-25416905371D}"/>
-    <hyperlink ref="C268" r:id="rId88" xr:uid="{49071A04-7D2C-4335-8F2D-C07A73C2ED46}"/>
-    <hyperlink ref="C269" r:id="rId89" xr:uid="{9F7D19E9-DDA7-4A3F-9D59-112358EBD9E0}"/>
-    <hyperlink ref="C271" r:id="rId90" xr:uid="{8234D9DE-2B88-4300-81AF-34B03109DDDA}"/>
-    <hyperlink ref="C270" r:id="rId91" xr:uid="{EA266D90-11D1-4D21-A8BF-CFB29B902E43}"/>
-    <hyperlink ref="C273" r:id="rId92" xr:uid="{512EF3E0-5603-4336-A1F7-B49DEE5BCDD3}"/>
-    <hyperlink ref="C266" r:id="rId93" xr:uid="{61421648-2752-404D-8392-A6973C6D1384}"/>
-    <hyperlink ref="C222" r:id="rId94" xr:uid="{15EC2F93-BB3A-4B62-8213-C821B3F23ED1}"/>
-    <hyperlink ref="C36" r:id="rId95" xr:uid="{810F4691-F177-4C87-AB91-7593A780FC4D}"/>
-    <hyperlink ref="C37" r:id="rId96" xr:uid="{A6BC95FC-933C-4853-80F0-A757FA055D0A}"/>
-    <hyperlink ref="C223" r:id="rId97" xr:uid="{E3DC44B5-133B-4B3D-94BA-FC35048FC75F}"/>
-    <hyperlink ref="C224" r:id="rId98" xr:uid="{394FA42B-65C2-418C-A6F8-712893C62D1B}"/>
-    <hyperlink ref="C225" r:id="rId99" xr:uid="{97083438-4D59-4400-909D-8780FDD486DD}"/>
-    <hyperlink ref="C226" r:id="rId100" xr:uid="{A71FD92F-5DC0-481E-8B13-AEFE8D01EE3D}"/>
-    <hyperlink ref="C227" r:id="rId101" xr:uid="{4F3DEFD2-DFEA-485E-9DA4-DF4AA90DC546}"/>
-    <hyperlink ref="C228" r:id="rId102" xr:uid="{A883D360-0D71-42DF-85E2-5E0F6BE34D47}"/>
-    <hyperlink ref="C232" r:id="rId103" xr:uid="{BB940023-875B-49F3-BB5A-8841D292B327}"/>
-    <hyperlink ref="C233" r:id="rId104" xr:uid="{41336D3B-DE94-4ECE-A917-2AFD7E906FB3}"/>
-    <hyperlink ref="C229" r:id="rId105" xr:uid="{DDE43479-E609-47AE-851F-DEFAEC028555}"/>
-    <hyperlink ref="C230" r:id="rId106" xr:uid="{38DB1A32-DA29-4158-85A4-693F4C968A99}"/>
-    <hyperlink ref="C231" r:id="rId107" xr:uid="{6DCB842C-7CB5-4442-9A76-04A35C9AB6D9}"/>
-    <hyperlink ref="C121" r:id="rId108" xr:uid="{BB79C0EA-0924-47F3-AA4A-2E45A9819642}"/>
-    <hyperlink ref="C38" r:id="rId109" xr:uid="{037CDD27-CA2C-41B8-912A-A06D1D605D8E}"/>
-    <hyperlink ref="C39" r:id="rId110" xr:uid="{FF6A1E36-6173-4C9D-9CBA-6C93A25E3B35}"/>
-    <hyperlink ref="C40" r:id="rId111" xr:uid="{C77462B1-65A0-4ACF-AC85-AE0A0F2E75F3}"/>
-    <hyperlink ref="C41" r:id="rId112" xr:uid="{8BDF7E3E-F770-4086-A437-B9095C96ECE0}"/>
-    <hyperlink ref="C42" r:id="rId113" xr:uid="{66B7BA22-5688-4926-8371-E1124D215116}"/>
-    <hyperlink ref="C43" r:id="rId114" xr:uid="{11360DA8-0A35-43CB-A0C1-973B175C4EEF}"/>
-    <hyperlink ref="C44" r:id="rId115" xr:uid="{602A74C8-570A-49F8-B587-0F34896339D8}"/>
-    <hyperlink ref="C45" r:id="rId116" xr:uid="{F9C3EA80-F066-4133-9C00-C1BA7AE1C0B7}"/>
-    <hyperlink ref="C46" r:id="rId117" xr:uid="{B158510D-1BCD-4300-BC99-1F238A5E7370}"/>
-    <hyperlink ref="C47" r:id="rId118" xr:uid="{0C0AE54E-B441-47C5-A757-93CF0E3934F2}"/>
-    <hyperlink ref="C48" r:id="rId119" xr:uid="{9D971AFD-F4DD-4C17-A2C4-88F079334F00}"/>
-    <hyperlink ref="C49" r:id="rId120" xr:uid="{B97E18DC-0FCA-46E4-8527-CE049E23B978}"/>
-    <hyperlink ref="C50" r:id="rId121" xr:uid="{BD4402B1-5B9C-4AB6-A3C5-4E80A8E2EC5D}"/>
-    <hyperlink ref="C51" r:id="rId122" xr:uid="{A80EFE5A-FA99-4E79-ABBE-D642C6CD7FA1}"/>
-    <hyperlink ref="C52" r:id="rId123" xr:uid="{3E220554-C045-443E-8C46-61552AE0FC97}"/>
-    <hyperlink ref="C145" r:id="rId124" xr:uid="{3BB8BA7A-8F25-42F0-9087-80A30399D4D7}"/>
-    <hyperlink ref="C146" r:id="rId125" xr:uid="{8CE5A08A-9DD7-4A1D-A70D-DD6045DBD308}"/>
-    <hyperlink ref="C147" r:id="rId126" xr:uid="{FB65DDD7-8995-4C4B-9966-1DF4E5009A5D}"/>
-    <hyperlink ref="C148" r:id="rId127" xr:uid="{5C13F391-9C3D-4DFE-BFA6-56D3CFFC3843}"/>
-    <hyperlink ref="C149" r:id="rId128" xr:uid="{1AF9C26F-2521-4F71-A969-8DD780FA220A}"/>
-    <hyperlink ref="C150" r:id="rId129" xr:uid="{C7974E80-8C5B-406A-A998-24C80C46041C}"/>
-    <hyperlink ref="C151" r:id="rId130" xr:uid="{5B8DE0B0-DE14-4831-96BA-319485DDA271}"/>
-    <hyperlink ref="C152" r:id="rId131" xr:uid="{4EA0531C-3893-4BF5-9956-395C37540608}"/>
-    <hyperlink ref="C153" r:id="rId132" xr:uid="{C11BC6EE-7E3F-42AC-9DFD-69631FF7535F}"/>
-    <hyperlink ref="C154" r:id="rId133" xr:uid="{719C9C7B-3EBE-4228-A435-8627717D7ADD}"/>
-    <hyperlink ref="C155" r:id="rId134" xr:uid="{BCB52D47-811D-4CB7-AEA7-59B387503024}"/>
-    <hyperlink ref="C156" r:id="rId135" xr:uid="{6C33F5E5-2E2D-4573-9E58-E785B04ACB9D}"/>
-    <hyperlink ref="C158" r:id="rId136" xr:uid="{BE45F618-2318-4CB8-8B2A-5CD0551B1F3C}"/>
-    <hyperlink ref="C159" r:id="rId137" xr:uid="{8351379E-1671-4F18-90B5-1D6852AA914B}"/>
-    <hyperlink ref="C160" r:id="rId138" xr:uid="{BAB750BD-5823-4CBC-902D-403FA494D8D1}"/>
-    <hyperlink ref="C289" r:id="rId139" xr:uid="{1A1B0C4E-D349-41BC-BBAE-10837FED784A}"/>
-    <hyperlink ref="C285" r:id="rId140" xr:uid="{26A51FE6-74B7-4AFA-B7DD-BCA4CD31AFB6}"/>
-    <hyperlink ref="C287" r:id="rId141" xr:uid="{56EE1A38-C4CC-4E01-92DD-B9143FD3BE34}"/>
-    <hyperlink ref="C288" r:id="rId142" xr:uid="{C502189C-AF10-401B-A39F-E42535C1A062}"/>
-    <hyperlink ref="C286" r:id="rId143" xr:uid="{F18592C2-F279-44B2-9AB0-18EEA190D5DC}"/>
-    <hyperlink ref="C157" r:id="rId144" xr:uid="{CF2DF039-0A48-47E5-99BD-16AFDA8405D1}"/>
-    <hyperlink ref="C8" r:id="rId145" xr:uid="{8B67C030-D631-4649-9F6A-BAEF3470DDA6}"/>
-    <hyperlink ref="C299" r:id="rId146" xr:uid="{BDE6903E-5B8B-4958-9A12-2FC0EB20CF2D}"/>
-    <hyperlink ref="C300" r:id="rId147" xr:uid="{01EEC629-7B85-4CCD-8058-E7386B192222}"/>
-    <hyperlink ref="C302" r:id="rId148" xr:uid="{B598D957-573E-42E8-9119-6C0BDAB7AD98}"/>
-    <hyperlink ref="C301" r:id="rId149" xr:uid="{697A114A-7F88-4485-8979-D346F50A1EE4}"/>
-    <hyperlink ref="C303" r:id="rId150" xr:uid="{5CF8FF02-F3FD-4278-A6B0-26B0720A6E6B}"/>
-    <hyperlink ref="C304" r:id="rId151" xr:uid="{6DCA1AEC-F7A7-46C7-B994-FBBB992FB499}"/>
-    <hyperlink ref="C305" r:id="rId152" xr:uid="{94C39B30-AF32-45FB-997F-4CF291338CF2}"/>
-    <hyperlink ref="C9" r:id="rId153" xr:uid="{2380F1AC-2670-41C0-B744-6F4587DBF931}"/>
-    <hyperlink ref="C10" r:id="rId154" xr:uid="{16BBA4FA-7C5D-4148-9D0E-54AFAB25B578}"/>
-    <hyperlink ref="C11" r:id="rId155" xr:uid="{C6C8A50C-71B9-4AA5-93C4-89DB670E42CC}"/>
-    <hyperlink ref="C75" r:id="rId156" xr:uid="{A2075FE9-BED5-480E-9C75-63E134BC8727}"/>
-    <hyperlink ref="C197" r:id="rId157" xr:uid="{CA7E4400-82EE-4B3C-A998-5DBA4CAF15EA}"/>
+    <hyperlink ref="C22" r:id="rId3" xr:uid="{20733D4E-76EF-4D15-A191-DA273D019F1C}"/>
+    <hyperlink ref="C24" r:id="rId4" xr:uid="{8848D822-3821-4FB6-8AD3-8B584E94883B}"/>
+    <hyperlink ref="C340" r:id="rId5" xr:uid="{06B84589-7D92-4C6A-A1EC-D7F163E0D0DD}"/>
+    <hyperlink ref="C339" r:id="rId6" xr:uid="{2CDCECDC-EC23-45B2-83C3-6D858FBA83A4}"/>
+    <hyperlink ref="C338" r:id="rId7" xr:uid="{D66CABB6-8C01-408D-B0E5-66C569EA9218}"/>
+    <hyperlink ref="C337" r:id="rId8" xr:uid="{B8971A20-58A8-4C22-A9E8-91E87196AB83}"/>
+    <hyperlink ref="C336" r:id="rId9" xr:uid="{1EA17FF3-8048-41C4-823F-0DA5263637DC}"/>
+    <hyperlink ref="C335" r:id="rId10" xr:uid="{7AD84014-6533-40E3-9D98-4A265A3FDBD4}"/>
+    <hyperlink ref="C334" r:id="rId11" xr:uid="{B84975E4-7A1A-42CD-A0A0-537634E54280}"/>
+    <hyperlink ref="C333" r:id="rId12" xr:uid="{4200CE26-D6ED-4E3C-9775-C7598E4B6F49}"/>
+    <hyperlink ref="C40" r:id="rId13" xr:uid="{DE12AE35-6DEA-463D-B53F-2212C88645DB}"/>
+    <hyperlink ref="C43" r:id="rId14" xr:uid="{3B00C787-BB82-49CC-8A95-41EF4467A59B}"/>
+    <hyperlink ref="C72" r:id="rId15" xr:uid="{2AE76950-5324-4300-995E-5106A02D8E1B}"/>
+    <hyperlink ref="C77" r:id="rId16" xr:uid="{2D05523D-21DF-4F93-B581-B4A62EA2310C}"/>
+    <hyperlink ref="C76" r:id="rId17" xr:uid="{93E442DC-7068-437C-A8CE-29140B51D4A5}"/>
+    <hyperlink ref="C78" r:id="rId18" xr:uid="{8A555388-3D3D-4DF3-8F65-6B122CF52D40}"/>
+    <hyperlink ref="C79" r:id="rId19" xr:uid="{AF42E519-D7E9-4481-BCC9-2BC44CAEF483}"/>
+    <hyperlink ref="C80" r:id="rId20" xr:uid="{A5D2BDE3-4300-44D9-85CC-C36E56697508}"/>
+    <hyperlink ref="C81" r:id="rId21" xr:uid="{0EBE1D87-4A83-4F86-A580-529D6A6D6ADD}"/>
+    <hyperlink ref="C82" r:id="rId22" xr:uid="{D203E76E-29B6-4FAC-8DDF-41834DDFAB9F}"/>
+    <hyperlink ref="C88" r:id="rId23" xr:uid="{B86817D4-9E10-4D5C-A26A-EDF200C95CCD}"/>
+    <hyperlink ref="C99" r:id="rId24" xr:uid="{5E37B822-E937-4EA5-943F-4EEEA243B407}"/>
+    <hyperlink ref="C104" r:id="rId25" xr:uid="{5BABD35C-A539-45C6-BCC5-D1110132BD22}"/>
+    <hyperlink ref="C105" r:id="rId26" xr:uid="{94F74941-3E3B-4CB6-9101-B175F232B080}"/>
+    <hyperlink ref="C124" r:id="rId27" xr:uid="{516F9274-1601-4712-A989-FCCE247FC4E7}"/>
+    <hyperlink ref="C132" r:id="rId28" xr:uid="{2FA531D4-566E-4D78-99B3-CB6858F708F0}"/>
+    <hyperlink ref="C119" r:id="rId29" xr:uid="{BD966A3C-FFB2-48D6-A450-18F764AFF163}"/>
+    <hyperlink ref="C120" r:id="rId30" xr:uid="{40BACF63-FB50-44BA-9095-10B8796E4BE6}"/>
+    <hyperlink ref="C121" r:id="rId31" xr:uid="{821F58CC-BF96-4CA9-9FB2-A0F7FFCAFB35}"/>
+    <hyperlink ref="C122" r:id="rId32" xr:uid="{7604A04A-9CAD-433F-BE86-8E29D0ABDADB}"/>
+    <hyperlink ref="C123" r:id="rId33" xr:uid="{3BFDFFE0-C278-4A9B-B3AB-4797EB1254B3}"/>
+    <hyperlink ref="C136" r:id="rId34" xr:uid="{EE28E420-01EF-44B6-B677-A650514BEB32}"/>
+    <hyperlink ref="C138" r:id="rId35" xr:uid="{A395A8DF-3B2F-4066-A368-7DF3E8B68D5A}"/>
+    <hyperlink ref="C140" r:id="rId36" xr:uid="{2C402ADD-A9D7-4E73-9A47-00F715C5F723}"/>
+    <hyperlink ref="C198" r:id="rId37" xr:uid="{E1189F8B-D001-4C35-AA5B-0B8D78BC5764}"/>
+    <hyperlink ref="C174" r:id="rId38" xr:uid="{26D74A8A-C77D-4802-96E8-9CB5B9362A67}"/>
+    <hyperlink ref="C165" r:id="rId39" xr:uid="{EAA57945-F0B4-415F-92EC-8E043DA4011F}"/>
+    <hyperlink ref="C166" r:id="rId40" xr:uid="{D04D35D1-1A61-44A9-97FC-CF35B7483BA0}"/>
+    <hyperlink ref="C167" r:id="rId41" xr:uid="{DF4A7D14-251A-4379-A2DF-F79F25D5631B}"/>
+    <hyperlink ref="C168" r:id="rId42" xr:uid="{85EA1E54-06CF-42DF-B863-E17872EC7F9E}"/>
+    <hyperlink ref="C169" r:id="rId43" xr:uid="{6B74270E-8219-4E30-90C0-C8F8BB0F233E}"/>
+    <hyperlink ref="C170" r:id="rId44" xr:uid="{3B808E52-8245-42C5-8AB1-371B3426AB46}"/>
+    <hyperlink ref="C171" r:id="rId45" xr:uid="{57BE5715-6EB8-48AD-9D8E-68D2A2C1AC45}"/>
+    <hyperlink ref="C172" r:id="rId46" xr:uid="{F86C6EF3-29C2-4A55-B804-07AAADD2281A}"/>
+    <hyperlink ref="C173" r:id="rId47" xr:uid="{F316FF57-6B3C-4B4C-8570-0821DD015CA8}"/>
+    <hyperlink ref="C194" r:id="rId48" xr:uid="{627ADE43-952B-43B7-B0B5-14646496C762}"/>
+    <hyperlink ref="C193" r:id="rId49" xr:uid="{3AE9DF49-D95E-4C0B-81D9-2A6FBBF188B2}"/>
+    <hyperlink ref="C192" r:id="rId50" xr:uid="{BF206D77-8B0F-443A-AA07-E839166658AE}"/>
+    <hyperlink ref="C143" r:id="rId51" xr:uid="{A374E38A-D2A4-492A-8A27-453DB919A65E}"/>
+    <hyperlink ref="C222" r:id="rId52" xr:uid="{F8E60DA5-82F0-44D7-9BE0-1ECA3A1592D0}"/>
+    <hyperlink ref="C225" r:id="rId53" xr:uid="{B7D784B0-EB2B-4CD6-A69D-91AD2CF7650B}"/>
+    <hyperlink ref="C227" r:id="rId54" xr:uid="{345F84E1-725F-4245-8DAA-513D09173FA4}"/>
+    <hyperlink ref="C231" r:id="rId55" xr:uid="{006E2639-98C6-4267-B7E6-2D637FA75DB7}"/>
+    <hyperlink ref="C202" r:id="rId56" xr:uid="{3BAC8BD3-2588-4FE6-AEAD-45FF6DEDF142}"/>
+    <hyperlink ref="C239" r:id="rId57" xr:uid="{EFDA4C91-3EF0-4AE8-B57A-B62EBE338CF7}"/>
+    <hyperlink ref="C223" r:id="rId58" xr:uid="{17119B19-6319-4464-B49B-F5E05C0FBF16}"/>
+    <hyperlink ref="C224" r:id="rId59" xr:uid="{C186F788-2029-44BF-9BD8-2CEC23AFAFFB}"/>
+    <hyperlink ref="C243" r:id="rId60" xr:uid="{C992E7AC-77D1-4580-9587-D5DD3454903E}"/>
+    <hyperlink ref="C244" r:id="rId61" xr:uid="{72118CFF-73CF-44CE-824E-2C7A6FEC993B}"/>
+    <hyperlink ref="C276" r:id="rId62" xr:uid="{742B394F-41B4-4BD8-A7A1-5814B9A6F4B0}"/>
+    <hyperlink ref="C277" r:id="rId63" xr:uid="{4196C746-9A38-4CC2-9D9B-E9BD1DCB665D}"/>
+    <hyperlink ref="C278" r:id="rId64" xr:uid="{2A9F81E4-8C6A-4870-A6CC-9D02518EEC2C}"/>
+    <hyperlink ref="C279" r:id="rId65" xr:uid="{918A3F4A-38CF-48DC-B25E-8F8206F6A21A}"/>
+    <hyperlink ref="C274" r:id="rId66" xr:uid="{69C00299-FCDF-4809-9709-4758F63AA450}"/>
+    <hyperlink ref="C280" r:id="rId67" xr:uid="{8EEB60CE-4C22-48E8-9948-99D3F7910A9C}"/>
+    <hyperlink ref="C281" r:id="rId68" xr:uid="{AEBCC0BF-1011-4EC2-BDC2-FBC699536B01}"/>
+    <hyperlink ref="C282" r:id="rId69" xr:uid="{2BA6B95C-F5B6-492C-8DAD-FEB98442F16B}"/>
+    <hyperlink ref="C284" r:id="rId70" xr:uid="{996F9E28-A976-4136-9509-BA0FD9AFC609}"/>
+    <hyperlink ref="C285" r:id="rId71" xr:uid="{DC5D5DB2-0B42-4B48-82C1-B0B6CFBC6E53}"/>
+    <hyperlink ref="C286" r:id="rId72" xr:uid="{3FB19267-D7AF-4689-B824-E43DC189BD41}"/>
+    <hyperlink ref="C304" r:id="rId73" xr:uid="{7DCD7B89-333E-475A-86FC-B6C842E51B32}"/>
+    <hyperlink ref="C305" r:id="rId74" xr:uid="{DD6EA494-FA8C-4FA3-AFDA-3AAB807783C4}"/>
+    <hyperlink ref="C307" r:id="rId75" xr:uid="{FD57C63E-4A9E-44F3-A68D-7D89331A239F}"/>
+    <hyperlink ref="C310" r:id="rId76" xr:uid="{461E749D-72B1-43DA-AC45-1276B46CDE71}"/>
+    <hyperlink ref="C287" r:id="rId77" xr:uid="{10F07EE6-12D1-49B1-BE4D-0B960E4AB8C8}"/>
+    <hyperlink ref="C288" r:id="rId78" xr:uid="{B9D6B3F9-6330-475B-A5CB-C68860BF8F7F}"/>
+    <hyperlink ref="C289" r:id="rId79" xr:uid="{59EE37E4-067E-4B14-B37D-1A2BA9000586}"/>
+    <hyperlink ref="C290" r:id="rId80" xr:uid="{568FE7CE-3364-4CD6-AEFC-687097A104FF}"/>
+    <hyperlink ref="C291" r:id="rId81" xr:uid="{D92E157D-9FF5-4554-A712-3E76586EA7A9}"/>
+    <hyperlink ref="C292" r:id="rId82" xr:uid="{ADFB8930-804D-438B-BC6A-C3563EFA36F0}"/>
+    <hyperlink ref="C293" r:id="rId83" xr:uid="{7B2C9358-08A3-4414-85F3-1F82D40BCC3A}"/>
+    <hyperlink ref="C294" r:id="rId84" xr:uid="{C56446CA-EDC5-4121-A19D-ECBA57E3D5E0}"/>
+    <hyperlink ref="C302" r:id="rId85" xr:uid="{13EF1E40-B469-438B-9385-2AB7F8E3DEA1}"/>
+    <hyperlink ref="C295" r:id="rId86" xr:uid="{87150E4D-68B3-4113-88EA-A4FF14C6760A}"/>
+    <hyperlink ref="C297" r:id="rId87" xr:uid="{18681F76-D099-492A-A200-25416905371D}"/>
+    <hyperlink ref="C298" r:id="rId88" xr:uid="{49071A04-7D2C-4335-8F2D-C07A73C2ED46}"/>
+    <hyperlink ref="C299" r:id="rId89" xr:uid="{9F7D19E9-DDA7-4A3F-9D59-112358EBD9E0}"/>
+    <hyperlink ref="C301" r:id="rId90" xr:uid="{8234D9DE-2B88-4300-81AF-34B03109DDDA}"/>
+    <hyperlink ref="C300" r:id="rId91" xr:uid="{EA266D90-11D1-4D21-A8BF-CFB29B902E43}"/>
+    <hyperlink ref="C303" r:id="rId92" xr:uid="{512EF3E0-5603-4336-A1F7-B49DEE5BCDD3}"/>
+    <hyperlink ref="C296" r:id="rId93" xr:uid="{61421648-2752-404D-8392-A6973C6D1384}"/>
+    <hyperlink ref="C252" r:id="rId94" xr:uid="{15EC2F93-BB3A-4B62-8213-C821B3F23ED1}"/>
+    <hyperlink ref="C45" r:id="rId95" xr:uid="{810F4691-F177-4C87-AB91-7593A780FC4D}"/>
+    <hyperlink ref="C46" r:id="rId96" xr:uid="{A6BC95FC-933C-4853-80F0-A757FA055D0A}"/>
+    <hyperlink ref="C253" r:id="rId97" xr:uid="{E3DC44B5-133B-4B3D-94BA-FC35048FC75F}"/>
+    <hyperlink ref="C254" r:id="rId98" xr:uid="{394FA42B-65C2-418C-A6F8-712893C62D1B}"/>
+    <hyperlink ref="C255" r:id="rId99" xr:uid="{97083438-4D59-4400-909D-8780FDD486DD}"/>
+    <hyperlink ref="C256" r:id="rId100" xr:uid="{A71FD92F-5DC0-481E-8B13-AEFE8D01EE3D}"/>
+    <hyperlink ref="C257" r:id="rId101" xr:uid="{4F3DEFD2-DFEA-485E-9DA4-DF4AA90DC546}"/>
+    <hyperlink ref="C258" r:id="rId102" xr:uid="{A883D360-0D71-42DF-85E2-5E0F6BE34D47}"/>
+    <hyperlink ref="C262" r:id="rId103" xr:uid="{BB940023-875B-49F3-BB5A-8841D292B327}"/>
+    <hyperlink ref="C263" r:id="rId104" xr:uid="{41336D3B-DE94-4ECE-A917-2AFD7E906FB3}"/>
+    <hyperlink ref="C259" r:id="rId105" xr:uid="{DDE43479-E609-47AE-851F-DEFAEC028555}"/>
+    <hyperlink ref="C260" r:id="rId106" xr:uid="{38DB1A32-DA29-4158-85A4-693F4C968A99}"/>
+    <hyperlink ref="C261" r:id="rId107" xr:uid="{6DCB842C-7CB5-4442-9A76-04A35C9AB6D9}"/>
+    <hyperlink ref="C133" r:id="rId108" xr:uid="{BB79C0EA-0924-47F3-AA4A-2E45A9819642}"/>
+    <hyperlink ref="C47" r:id="rId109" xr:uid="{037CDD27-CA2C-41B8-912A-A06D1D605D8E}"/>
+    <hyperlink ref="C48" r:id="rId110" xr:uid="{FF6A1E36-6173-4C9D-9CBA-6C93A25E3B35}"/>
+    <hyperlink ref="C49" r:id="rId111" xr:uid="{C77462B1-65A0-4ACF-AC85-AE0A0F2E75F3}"/>
+    <hyperlink ref="C50" r:id="rId112" xr:uid="{8BDF7E3E-F770-4086-A437-B9095C96ECE0}"/>
+    <hyperlink ref="C51" r:id="rId113" xr:uid="{66B7BA22-5688-4926-8371-E1124D215116}"/>
+    <hyperlink ref="C52" r:id="rId114" xr:uid="{11360DA8-0A35-43CB-A0C1-973B175C4EEF}"/>
+    <hyperlink ref="C53" r:id="rId115" xr:uid="{602A74C8-570A-49F8-B587-0F34896339D8}"/>
+    <hyperlink ref="C54" r:id="rId116" xr:uid="{F9C3EA80-F066-4133-9C00-C1BA7AE1C0B7}"/>
+    <hyperlink ref="C55" r:id="rId117" xr:uid="{B158510D-1BCD-4300-BC99-1F238A5E7370}"/>
+    <hyperlink ref="C56" r:id="rId118" xr:uid="{0C0AE54E-B441-47C5-A757-93CF0E3934F2}"/>
+    <hyperlink ref="C57" r:id="rId119" xr:uid="{9D971AFD-F4DD-4C17-A2C4-88F079334F00}"/>
+    <hyperlink ref="C60" r:id="rId120" xr:uid="{B97E18DC-0FCA-46E4-8527-CE049E23B978}"/>
+    <hyperlink ref="C61" r:id="rId121" xr:uid="{BD4402B1-5B9C-4AB6-A3C5-4E80A8E2EC5D}"/>
+    <hyperlink ref="C62" r:id="rId122" xr:uid="{A80EFE5A-FA99-4E79-ABBE-D642C6CD7FA1}"/>
+    <hyperlink ref="C64" r:id="rId123" xr:uid="{3E220554-C045-443E-8C46-61552AE0FC97}"/>
+    <hyperlink ref="C175" r:id="rId124" xr:uid="{3BB8BA7A-8F25-42F0-9087-80A30399D4D7}"/>
+    <hyperlink ref="C176" r:id="rId125" xr:uid="{8CE5A08A-9DD7-4A1D-A70D-DD6045DBD308}"/>
+    <hyperlink ref="C177" r:id="rId126" xr:uid="{FB65DDD7-8995-4C4B-9966-1DF4E5009A5D}"/>
+    <hyperlink ref="C178" r:id="rId127" xr:uid="{5C13F391-9C3D-4DFE-BFA6-56D3CFFC3843}"/>
+    <hyperlink ref="C179" r:id="rId128" xr:uid="{1AF9C26F-2521-4F71-A969-8DD780FA220A}"/>
+    <hyperlink ref="C180" r:id="rId129" xr:uid="{C7974E80-8C5B-406A-A998-24C80C46041C}"/>
+    <hyperlink ref="C181" r:id="rId130" xr:uid="{5B8DE0B0-DE14-4831-96BA-319485DDA271}"/>
+    <hyperlink ref="C182" r:id="rId131" xr:uid="{4EA0531C-3893-4BF5-9956-395C37540608}"/>
+    <hyperlink ref="C183" r:id="rId132" xr:uid="{C11BC6EE-7E3F-42AC-9DFD-69631FF7535F}"/>
+    <hyperlink ref="C184" r:id="rId133" xr:uid="{719C9C7B-3EBE-4228-A435-8627717D7ADD}"/>
+    <hyperlink ref="C185" r:id="rId134" xr:uid="{BCB52D47-811D-4CB7-AEA7-59B387503024}"/>
+    <hyperlink ref="C186" r:id="rId135" xr:uid="{6C33F5E5-2E2D-4573-9E58-E785B04ACB9D}"/>
+    <hyperlink ref="C188" r:id="rId136" xr:uid="{BE45F618-2318-4CB8-8B2A-5CD0551B1F3C}"/>
+    <hyperlink ref="C189" r:id="rId137" xr:uid="{8351379E-1671-4F18-90B5-1D6852AA914B}"/>
+    <hyperlink ref="C190" r:id="rId138" xr:uid="{BAB750BD-5823-4CBC-902D-403FA494D8D1}"/>
+    <hyperlink ref="C331" r:id="rId139" xr:uid="{1A1B0C4E-D349-41BC-BBAE-10837FED784A}"/>
+    <hyperlink ref="C325" r:id="rId140" xr:uid="{26A51FE6-74B7-4AFA-B7DD-BCA4CD31AFB6}"/>
+    <hyperlink ref="C327" r:id="rId141" xr:uid="{56EE1A38-C4CC-4E01-92DD-B9143FD3BE34}"/>
+    <hyperlink ref="C328" r:id="rId142" xr:uid="{C502189C-AF10-401B-A39F-E42535C1A062}"/>
+    <hyperlink ref="C326" r:id="rId143" xr:uid="{F18592C2-F279-44B2-9AB0-18EEA190D5DC}"/>
+    <hyperlink ref="C187" r:id="rId144" xr:uid="{CF2DF039-0A48-47E5-99BD-16AFDA8405D1}"/>
+    <hyperlink ref="C17" r:id="rId145" xr:uid="{8B67C030-D631-4649-9F6A-BAEF3470DDA6}"/>
+    <hyperlink ref="C341" r:id="rId146" xr:uid="{BDE6903E-5B8B-4958-9A12-2FC0EB20CF2D}"/>
+    <hyperlink ref="C342" r:id="rId147" xr:uid="{01EEC629-7B85-4CCD-8058-E7386B192222}"/>
+    <hyperlink ref="C344" r:id="rId148" xr:uid="{B598D957-573E-42E8-9119-6C0BDAB7AD98}"/>
+    <hyperlink ref="C343" r:id="rId149" xr:uid="{697A114A-7F88-4485-8979-D346F50A1EE4}"/>
+    <hyperlink ref="C345" r:id="rId150" xr:uid="{5CF8FF02-F3FD-4278-A6B0-26B0720A6E6B}"/>
+    <hyperlink ref="C346" r:id="rId151" xr:uid="{6DCA1AEC-F7A7-46C7-B994-FBBB992FB499}"/>
+    <hyperlink ref="C347" r:id="rId152" xr:uid="{94C39B30-AF32-45FB-997F-4CF291338CF2}"/>
+    <hyperlink ref="C18" r:id="rId153" xr:uid="{2380F1AC-2670-41C0-B744-6F4587DBF931}"/>
+    <hyperlink ref="C19" r:id="rId154" xr:uid="{16BBA4FA-7C5D-4148-9D0E-54AFAB25B578}"/>
+    <hyperlink ref="C20" r:id="rId155" xr:uid="{C6C8A50C-71B9-4AA5-93C4-89DB670E42CC}"/>
+    <hyperlink ref="C87" r:id="rId156" xr:uid="{A2075FE9-BED5-480E-9C75-63E134BC8727}"/>
+    <hyperlink ref="C226" r:id="rId157" xr:uid="{CA7E4400-82EE-4B3C-A998-5DBA4CAF15EA}"/>
+    <hyperlink ref="C7" r:id="rId158" xr:uid="{54FA8CF0-29AE-4AE3-A5AD-95160DCD6381}"/>
+    <hyperlink ref="C8" r:id="rId159" xr:uid="{2AB49368-260E-46BE-B5FD-EF6E2F87803F}"/>
+    <hyperlink ref="C9" r:id="rId160" xr:uid="{1737C84A-F447-4D0D-82AE-560CA81DBC40}"/>
+    <hyperlink ref="C10" r:id="rId161" xr:uid="{6C46BC54-00E7-47ED-8AA4-9B30BCAA0514}"/>
+    <hyperlink ref="C11" r:id="rId162" xr:uid="{2F3FA999-E35A-4E1C-B155-F1B562FCF3BF}"/>
+    <hyperlink ref="C12" r:id="rId163" xr:uid="{B6243AB2-3258-4B33-B70B-D16750C4D775}"/>
+    <hyperlink ref="C13" r:id="rId164" xr:uid="{8CEFDED7-A2A6-4E9E-B367-E1068031D9C4}"/>
+    <hyperlink ref="C14" r:id="rId165" xr:uid="{4D9DB436-A199-42AF-B4C8-11B6CC78CA9A}"/>
+    <hyperlink ref="C15" r:id="rId166" xr:uid="{69E3824A-37EA-4B1E-B233-7572303D4E3E}"/>
+    <hyperlink ref="C16" r:id="rId167" xr:uid="{FBBDBDFE-25F6-475E-B13F-8A868741CDFF}"/>
+    <hyperlink ref="C145" r:id="rId168" xr:uid="{9808F1F5-A9EE-4567-9AF8-B628E209D3FE}"/>
+    <hyperlink ref="C146" r:id="rId169" xr:uid="{0C612E14-5EDE-4A02-8C57-6259D7E3567C}"/>
+    <hyperlink ref="C147" r:id="rId170" xr:uid="{608CC549-4F2D-42D9-8766-158928924E4E}"/>
+    <hyperlink ref="C148" r:id="rId171" xr:uid="{FD75ADC7-C52C-4D1E-982D-F6704CF3A5BD}"/>
+    <hyperlink ref="C149" r:id="rId172" xr:uid="{7F051C2A-6B4A-466B-97B2-5B221503F955}"/>
+    <hyperlink ref="C150" r:id="rId173" xr:uid="{E9D2274C-8183-4843-AB30-8D9800748E98}"/>
+    <hyperlink ref="C151" r:id="rId174" xr:uid="{FF79A60E-D283-49C8-9D3E-C53154217A0D}"/>
+    <hyperlink ref="C152" r:id="rId175" xr:uid="{80EE03E6-53C4-4B82-85EA-BEA6B35ADDE9}"/>
+    <hyperlink ref="C153" r:id="rId176" xr:uid="{5247337D-7D5F-469A-9E5E-0A162FE3DF6F}"/>
+    <hyperlink ref="C154" r:id="rId177" xr:uid="{700ED880-1AD1-48E6-A1AC-C96C87740957}"/>
+    <hyperlink ref="C155" r:id="rId178" xr:uid="{6B6FB428-670F-4883-B35D-28A09501A46F}"/>
+    <hyperlink ref="C156" r:id="rId179" xr:uid="{77F2F443-C6E9-4697-A615-1B5E9F2D1BCE}"/>
+    <hyperlink ref="C157" r:id="rId180" xr:uid="{A3EAA7A9-5124-4794-B65A-B32C00B2A615}"/>
+    <hyperlink ref="C158" r:id="rId181" xr:uid="{E329330C-15CE-4B6E-AC75-3108077B9F58}"/>
+    <hyperlink ref="C159" r:id="rId182" xr:uid="{FB66326C-E163-4AF3-9515-772421E8C61A}"/>
+    <hyperlink ref="C63" r:id="rId183" xr:uid="{F882E1D5-3199-4AFE-A97D-A46F9DCA728A}"/>
+    <hyperlink ref="C160" r:id="rId184" xr:uid="{3BB08446-32B8-4B46-8398-2005013B0FAE}"/>
+    <hyperlink ref="C161" r:id="rId185" xr:uid="{B0D1A20C-2A8C-409C-93C2-5CDB0904D7D0}"/>
+    <hyperlink ref="C312" r:id="rId186" xr:uid="{8823278D-2110-46D5-934C-474F2E408342}"/>
+    <hyperlink ref="C311" r:id="rId187" xr:uid="{F84979B2-9996-4270-8C1A-1ECFBF17DED1}"/>
+    <hyperlink ref="C313" r:id="rId188" xr:uid="{58F35E3B-6087-4FB8-83B7-769FFDC5850E}"/>
+    <hyperlink ref="C314" r:id="rId189" xr:uid="{9A424A3F-B371-4770-A928-4CCB646BB40A}"/>
+    <hyperlink ref="C315" r:id="rId190" xr:uid="{29D387D0-4254-417E-B0B6-6A16EAF8674D}"/>
+    <hyperlink ref="C58" r:id="rId191" xr:uid="{27922B1D-AFDC-4F3F-A904-7C0AE453DFC2}"/>
+    <hyperlink ref="C59" r:id="rId192" xr:uid="{D322E7BE-CD92-42F5-A0B7-131945604AFB}"/>
+    <hyperlink ref="C142" r:id="rId193" xr:uid="{D6CDC188-19CD-4B4B-8B1C-0FFC05AF9724}"/>
+    <hyperlink ref="C316" r:id="rId194" xr:uid="{7CF49523-16C0-4E9B-B254-8E83A47D25B7}"/>
+    <hyperlink ref="C197" r:id="rId195" xr:uid="{1B19AAD9-65BA-4D70-9AE4-A4CE7CC27AC5}"/>
+    <hyperlink ref="C317" r:id="rId196" xr:uid="{EF5ADB02-C4DF-4077-AD21-1ADC0A346494}"/>
+    <hyperlink ref="C318" r:id="rId197" xr:uid="{3D8DA082-58BA-4CE4-ADF2-A53ED8D23CE6}"/>
+    <hyperlink ref="C319" r:id="rId198" xr:uid="{E0E2F5ED-E65D-4AA9-8C5B-A6871BD1B6F0}"/>
+    <hyperlink ref="C320" r:id="rId199" xr:uid="{21B67785-DBB0-4E59-B035-1C8802C3E0CD}"/>
+    <hyperlink ref="C249" r:id="rId200" xr:uid="{8C3C7D60-8E58-46E5-80E8-57CD214AECF5}"/>
+    <hyperlink ref="C329" r:id="rId201" xr:uid="{6C3646D4-BFB0-44BC-A508-994334B6EB2B}"/>
+    <hyperlink ref="C330" r:id="rId202" xr:uid="{47AD3E1D-8DDF-4F4E-A9B5-5A59CF4F93F3}"/>
+    <hyperlink ref="C348" r:id="rId203" xr:uid="{8090E2EC-E6F8-4291-BA77-69A8CF79682A}"/>
+    <hyperlink ref="C349" r:id="rId204" xr:uid="{889EABDA-3F7F-45FA-A5B2-513F4012909D}"/>
+    <hyperlink ref="C350" r:id="rId205" xr:uid="{0C9895A7-30E7-447F-9748-5391F5D96EC0}"/>
+    <hyperlink ref="C351" r:id="rId206" xr:uid="{AE5C96F8-ADB2-4263-9BDF-23491BD1ED9D}"/>
+    <hyperlink ref="C352" r:id="rId207" xr:uid="{D2A304C3-A43B-4268-9E36-F40EE47D46F0}"/>
+    <hyperlink ref="C353" r:id="rId208" xr:uid="{CB58376D-EEA5-4861-B959-BF9DA85A93BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId158"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId209"/>
 </worksheet>
 </file>